--- a/data/trans_orig/IP28_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96912</t>
+          <t>97105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92258</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191882</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197290</t>
+          <t>197289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80302</t>
+          <t>81409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80574</t>
+          <t>80587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164129</t>
+          <t>164645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169363</t>
+          <t>169368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62598</t>
+          <t>63200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91952</t>
+          <t>92575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158333</t>
+          <t>157290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164142</t>
+          <t>164139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192955</t>
+          <t>192931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197410</t>
+          <t>197408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192777</t>
+          <t>192491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198868</t>
+          <t>198822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387594</t>
+          <t>388165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395477</t>
+          <t>395623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95955</t>
+          <t>96074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102296</t>
+          <t>102277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123444</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221923</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228338</t>
+          <t>228330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140917</t>
+          <t>141420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615225</t>
+          <t>614374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>624506</t>
+          <t>623968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663626</t>
+          <t>664112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672854</t>
+          <t>672899</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1281641</t>
+          <t>1281773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1295802</t>
+          <t>1295508</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77628</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80077</t>
+          <t>79885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160992</t>
+          <t>160592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166880</t>
+          <t>166858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81968</t>
+          <t>81978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82724</t>
+          <t>82287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167124</t>
+          <t>167028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172360</t>
+          <t>172347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72039</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72296</t>
+          <t>72094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146380</t>
+          <t>146029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152222</t>
+          <t>152185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178656</t>
+          <t>178932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186014</t>
+          <t>186022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197883</t>
+          <t>197944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204692</t>
+          <t>204785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>379853</t>
+          <t>380332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388950</t>
+          <t>389455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126832</t>
+          <t>126350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133068</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124434</t>
+          <t>124730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130406</t>
+          <t>130410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254270</t>
+          <t>254186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262692</t>
+          <t>262773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>46342</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117428</t>
+          <t>118082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597952</t>
+          <t>598708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609829</t>
+          <t>609976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>640046</t>
+          <t>640742</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651347</t>
+          <t>651521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1243737</t>
+          <t>1243157</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1259301</t>
+          <t>1258658</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91879</t>
+          <t>92270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193550</t>
+          <t>193560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>63456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>69220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127416</t>
+          <t>127405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195225</t>
+          <t>195340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201058</t>
+          <t>201037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182772</t>
+          <t>182668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380764</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387893</t>
+          <t>387790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112808</t>
+          <t>112903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121432</t>
+          <t>121430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126018</t>
+          <t>126024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236722</t>
+          <t>237088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243094</t>
+          <t>243119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115885</t>
+          <t>115787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595707</t>
+          <t>595269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603378</t>
+          <t>602914</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627314</t>
+          <t>627614</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>635098</t>
+          <t>635629</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1226354</t>
+          <t>1226320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1237164</t>
+          <t>1236938</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98438</t>
+          <t>98646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131788</t>
+          <t>131834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233418</t>
+          <t>233035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239493</t>
+          <t>239477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89336</t>
+          <t>89368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>91563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183830</t>
+          <t>183740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188858</t>
+          <t>188857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50329</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114250</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>210885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216760</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211205</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424113</t>
+          <t>424081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431507</t>
+          <t>431620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,82 +10025,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10506</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10546</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>110074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118594</t>
+          <t>118604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>161080</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>157737</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>162617</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>276864</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>271539</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>280079</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>161080</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>157619</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>162617</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>276864</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>271499</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>279879</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62627</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71525</t>
+          <t>71500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131967</t>
+          <t>132210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139882</t>
+          <t>139874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637612</t>
+          <t>638029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649665</t>
+          <t>649683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>732679</t>
+          <t>731529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>742259</t>
+          <t>741874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375010</t>
+          <t>1373500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1389639</t>
+          <t>1389432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
